--- a/output/pdf_financials_xlsx/DFN.xlsx
+++ b/output/pdf_financials_xlsx/DFN.xlsx
@@ -2168,37 +2168,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>30.286536</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>32.255534</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>53.675764</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>41.484759</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>31.499892</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>53.692474</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>64.774405</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>53.231516</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>102.292378</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>150.585035</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>286.407013</v>
       </c>
     </row>
     <row r="35">
@@ -2248,37 +2248,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>30.286536</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>32.255534</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>53.675764</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>41.484759</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>31.499892</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>53.692474</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>64.774405</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>53.231516</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>102.292378</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>150.585035</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>286.407013</v>
       </c>
     </row>
     <row r="37">
@@ -2734,31 +2734,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>392.324908</v>
+        <v>338.649144</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>533.538739</v>
+        <v>492.05398</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>550.918672</v>
+        <v>519.41878</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>618.19373</v>
+        <v>564.501256</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>765.097218</v>
+        <v>700.322813</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>783.844608</v>
+        <v>730.6130920000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>985.669546</v>
+        <v>883.377168</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1584.093779</v>
+        <v>1433.508744</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1731.495961</v>
+        <v>1445.088948</v>
       </c>
     </row>
     <row r="49">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
